--- a/extenbooks/S1405_extenbook.xlsx
+++ b/extenbooks/S1405_extenbook.xlsx
@@ -7728,7 +7728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A89"/>
+  <dimension ref="A1:A91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -7760,7 +7760,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>**DPR · Phase 5 · Ch 14 · Fig 14.14 · Authored 2026-05-18**</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -7770,327 +7770,327 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>## 1. Definition</t>
+          <t>**DPR · Phase 5 · Ch 14 · Fig 14.14 · Authored 2026-05-18**</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>HP(100)-filtered analogue of S1404 plus the two-era Phillips-form fitted</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>curves Shaikh reports in Appendix 14.2 (era 1: 1949-1982; era 2: 1994-2011).</t>
+          <t>## 1. Definition</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>HP(100)-filtered analogue of S1404 plus the two-era Phillips-form fitted</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>## 2. Why it matters</t>
+          <t>curves Shaikh reports in Appendix 14.2 (era 1: 1949-1982; era 2: 1994-2011).</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>The central empirical result of Chapter 14: a stable wage-share Phillips</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>curve in two segments, with the post-1983 segment shifted DOWN -- consistent</t>
+          <t>## 2. Why it matters</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>with the neoliberal attack on labor (critical intensity ~9% era 1 vs ~5-6%</t>
+          <t>The central empirical result of Chapter 14: a stable wage-share Phillips</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>era 2; corresponding "normal" unemployment ~5.9% vs ~4.2%).</t>
+          <t>curve in two segments, with the post-1983 segment shifted DOWN -- consistent</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>with the neoliberal attack on labor (critical intensity ~9% era 1 vs ~5-6%</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>## 3. Sources</t>
+          <t>era 2; corresponding "normal" unemployment ~5.9% vs ~4.2%).</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>| Subseries | Source |</t>
-        </is>
-      </c>
+      <c r="A19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>|---|---|</t>
+          <t>## 3. Sources</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>| S1405-A `gwshhp100` | Appendix 14.3 |</t>
+          <t>| Subseries | Source |</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>| S1405-B `ulintensityhp100` | Appendix 14.3 |</t>
+          <t>|---|---|</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>| S1405-FIT1 `GWSHHP100RAL8AF` | Appendix 14.3 (era-1 published constrained b=1 fit) |</t>
+          <t>| S1405-A `gwshhp100` | Appendix 14.3 |</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>| S1405-FIT2 `GWSHHP100RAL8BP1F` | Appendix 14.3 (era-2 published constrained b=1 fit) |</t>
+          <t>| S1405-B `ulintensityhp100` | Appendix 14.3 |</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>| S1405-FIT1 `GWSHHP100RAL8AF` | Appendix 14.3 (era-1 published constrained b=1 fit) |</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>## 4. Construction</t>
+          <t>| S1405-FIT2 `GWSHHP100RAL8BP1F` | Appendix 14.3 (era-2 published constrained b=1 fit) |</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Direct read-through of Appendix HP100 series and published fits.</t>
-        </is>
-      </c>
+      <c r="A27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PLUS the processor independently fits the Phillips form</t>
+          <t>## 4. Construction</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>`y = a + b * x^c` over each era window in TWO variants:</t>
+          <t>Direct read-through of Appendix HP100 series and published fits.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>- **constrained_b1**: `y = a + x^c` (Shaikh's published form, implicit b=1)</t>
+          <t>PLUS the processor independently fits the Phillips form</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>- **unconstrained**: free three-parameter `y = a + b * x^c`</t>
+          <t>`y = a + b * x^c` over each era window in TWO variants:</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1983-1993 transition omitted from both fits per Shaikh's convention</t>
+          <t>- **constrained_b1**: `y = a + x^c` (Shaikh's published form, implicit b=1)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>(Phase 4 Q4 resolution). Sidecar JSON `S1405_phillips_fits.json` records</t>
+          <t>- **unconstrained**: free three-parameter `y = a + b * x^c`</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>both variants plus an additional pre-2008 era-2 fit (1994-2007) for Phase 6</t>
+          <t>1983-1993 transition omitted from both fits per Shaikh's convention</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>regime-stability assessment.</t>
+          <t>(Phase 4 Q4 resolution). Sidecar JSON `S1405_phillips_fits.json` records</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>both variants plus an additional pre-2008 era-2 fit (1994-2007) for Phase 6</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>regime-stability assessment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>## 5. Year coverage</t>
         </is>
       </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>1949-2011.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>1949-2011.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>## 6. Units</t>
         </is>
       </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Decimal HP100 on both axes; Phillips parameters dimensionless.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>## 7. Caveats</t>
+          <t>Decimal HP100 on both axes; Phillips parameters dimensionless.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>1. **HP lambda=100** (Shaikh's annual default; Appendix 14.2 p. 893).</t>
-        </is>
-      </c>
+      <c r="A44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2. **Constrained vs unconstrained fits**: published reports a (C(1)) and c</t>
+          <t>## 7. Caveats</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (C(3)) under implicit b=1. Phase 5 emits both for transparency.</t>
+          <t>1. **HP lambda=100** (Shaikh's annual default; Appendix 14.2 p. 893).</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3. **1983-1993 transition**: omitted from primary fits.</t>
+          <t>2. **Constrained vs unconstrained fits**: published reports a (C(1)) and c</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr"/>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   (C(3)) under implicit b=1. Phase 5 emits both for transparency.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>## 8. Cross-references</t>
+          <t>3. **1983-1993 transition**: omitted from primary fits.</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>CD `S072`. Book p. 666-668. Published era-1: a=-1.026431, c=-0.010677,</t>
-        </is>
-      </c>
+      <c r="A50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>R²=0.931; era-2: a=-1.010996, c=-0.003709, R²=0.965.</t>
+          <t>## 8. Cross-references</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>CD `S072`. Book p. 666-668. Published era-1: a=-1.026431, c=-0.010677,</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>## 9. Validation expectation</t>
+          <t>R²=0.931; era-2: a=-1.010996, c=-0.003709, R²=0.965.</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>±1.0% pass-through on the time series; ±0.05 absolute on fitted (a, c)</t>
-        </is>
-      </c>
+      <c r="A54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>## 9. Validation expectation</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>±1.0% pass-through on the time series; ±0.05 absolute on fitted (a, c)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>parameters vs published.</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="4">
+    <row r="60">
+      <c r="A60" s="4">
         <f>== EPR: S1405_EPR.md ===</f>
         <v/>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t># S1405 — Extension Provenance Record</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr"/>
-    </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>**Ch 14 · Authored 2026-05-18**</t>
+          <t># S1405 — Extension Provenance Record</t>
         </is>
       </c>
     </row>
@@ -8100,167 +8100,177 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>## Classification</t>
+          <t>**Ch 14 · Authored 2026-05-18**</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>`content_type: time_series` · `construction: direct` (HP-filtered observed</t>
-        </is>
-      </c>
+      <c r="A64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>inputs + fitted curves). Extension via S1401/S1402 components, re-filtered</t>
+          <t>## Classification</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>over the full sample.</t>
+          <t>`content_type: time_series` · `construction: direct` (HP-filtered observed</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr"/>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>inputs + fitted curves). Extension via S1401/S1402 components, re-filtered</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>## Method</t>
+          <t>over the full sample.</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Phase 5: replicate the published constrained b=1 fits. Phase 6: re-fit on</t>
-        </is>
-      </c>
+      <c r="A69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1949-1982 and (extended) 1994-2024, plus a separate 1994-2007 era-2 fit for</t>
+          <t>## Method</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>regime-stability assessment per Q4 resolution.</t>
+          <t>Phase 5: replicate the published constrained b=1 fits. Phase 6: re-fit on</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr"/>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>1949-1982 and (extended) 1994-2024, plus a separate 1994-2007 era-2 fit for</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>## Dual Phillips fit</t>
+          <t>regime-stability assessment per Q4 resolution.</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>BOTH variants are emitted to `Technical/data/processed/S1405_phillips_fits.json`:</t>
-        </is>
-      </c>
+      <c r="A74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>- `constrained_b1`: replicates Shaikh's published form `y = a + x^c`</t>
+          <t>## Dual Phillips fit</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>- `unconstrained`: free three-parameter `y = a + b * x^c`</t>
+          <t>BOTH variants are emitted to `Technical/data/processed/S1405_phillips_fits.json`:</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Comparison documented in the validator report.</t>
+          <t>- `constrained_b1`: replicates Shaikh's published form `y = a + x^c`</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr"/>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>- `unconstrained`: free three-parameter `y = a + b * x^c`</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>Comparison documented in the validator report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
           <t>## No-Proxy / No-Synthetic disclosures</t>
         </is>
       </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Inherits from S1401 and S1402.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>## Failure-mode table</t>
+          <t>Inherits from S1401 and S1402.</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>| Mode | Trigger | Behaviour |</t>
-        </is>
-      </c>
+      <c r="A83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>|---|---|---|</t>
+          <t>## Failure-mode table</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>| curve_fit non-convergence | numerical | Returns `converged: false` with NaN params; doesn't fail pipeline |</t>
+          <t>| Mode | Trigger | Behaviour |</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>| era window has &lt; 4 obs | very short window | Returns `converged: false` |</t>
+          <t>|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr"/>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>| curve_fit non-convergence | numerical | Returns `converged: false` with NaN params; doesn't fail pipeline |</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>| era window has &lt; 4 obs | very short window | Returns `converged: false` |</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
           <t>## CD2 divergence pre-disclosure</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
+    <row r="91">
+      <c r="A91" t="inlineStr">
         <is>
           <t>Minor; CD2 only emitted scatter, not fits.</t>
         </is>
@@ -8729,11 +8739,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8756,76 +8766,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>HP(100)-Filtered Rate of Change of Wage Share vs Unemployment Intensity</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S1405_research.json", "adequacy_report": "Technical/docs/chapters/CH14_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S1405_DPR.md", "epr": "Technical/docs/series/S1405_EPR.md", "loader": "Technical/code/L01_loaders/L01_S1405_load.py", "processor": "Technical/code/P02_processors/P02_S1405_construct.py", "validator": "Technical/code/V03_validators/V03_S1405_validate.py", "processed": "Technical/data/processed/S1405.parquet", "chopped_csv": "Technical/chopped/S1405.csv", "extenbook_xlsx": "Technical/extenbooks/S1405_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-18T22:58:43.529185+00:00</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S1405_extenbook.xlsx
+++ b/extenbooks/S1405_extenbook.xlsx
@@ -7728,7 +7728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A91"/>
+  <dimension ref="A1:A92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -7760,7 +7760,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t>**Data Provenance Record · Ingestion stage · Chapter 14 · Figure 14.14 · Authored 2026-05-18**</t>
         </is>
       </c>
     </row>
@@ -7770,69 +7770,69 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>**DPR · Phase 5 · Ch 14 · Fig 14.14 · Authored 2026-05-18**</t>
+          <t>## 1. Definition</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>HP(100)-filtered (Hodrick-Prescott filter, smoothing parameter lambda=100) analogue of S1404 plus the two-era Phillips-form fitted</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>## 1. Definition</t>
+          <t>curves Shaikh reports in Appendix 14.2 (era 1: 1949-1982; era 2: 1994-2011).</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>HP(100)-filtered analogue of S1404 plus the two-era Phillips-form fitted</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>curves Shaikh reports in Appendix 14.2 (era 1: 1949-1982; era 2: 1994-2011).</t>
+          <t>## 2. Why it matters</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>The central empirical result of Chapter 14: a stable wage-share Phillips</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>## 2. Why it matters</t>
+          <t>curve in two segments, with the post-1983 segment shifted DOWN -- consistent</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>The central empirical result of Chapter 14: a stable wage-share Phillips</t>
+          <t>with the neoliberal attack on labor (critical intensity ~9% era 1 vs ~5-6%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>curve in two segments, with the post-1983 segment shifted DOWN -- consistent</t>
+          <t>era 2; corresponding "normal" unemployment ~5.9% vs ~4.2%).</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>with the neoliberal attack on labor (critical intensity ~9% era 1 vs ~5-6%</t>
-        </is>
-      </c>
+      <c r="A17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>era 2; corresponding "normal" unemployment ~5.9% vs ~4.2%).</t>
+          <t>## 3. Sources</t>
         </is>
       </c>
     </row>
@@ -7842,437 +7842,440 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>## 3. Sources</t>
+          <t>*Each series is built from sub-components identified by a suffix on the series ID (for example, S1405-A, S1405-B); they are listed below.*</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>| Subseries | Source |</t>
-        </is>
-      </c>
+      <c r="A21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>|---|---|</t>
+          <t>| Subseries | Source |</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>| S1405-A `gwshhp100` | Appendix 14.3 |</t>
+          <t>|---|---|</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>| S1405-B `ulintensityhp100` | Appendix 14.3 |</t>
+          <t>| S1405-A `gwshhp100` | Appendix 14.3 |</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>| S1405-FIT1 `GWSHHP100RAL8AF` | Appendix 14.3 (era-1 published constrained b=1 fit) |</t>
+          <t>| S1405-B `ulintensityhp100` | Appendix 14.3 |</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>| S1405-FIT1 `GWSHHP100RAL8AF` | Appendix 14.3 (era-1 published constrained b=1 fit) |</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>| S1405-FIT2 `GWSHHP100RAL8BP1F` | Appendix 14.3 (era-2 published constrained b=1 fit) |</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-    </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>## 4. Construction</t>
-        </is>
-      </c>
+      <c r="A28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Direct read-through of Appendix HP100 series and published fits.</t>
+          <t>## 4. Construction</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PLUS the processor independently fits the Phillips form</t>
+          <t>Direct read-through of Appendix HP100 series and published fits.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>`y = a + b * x^c` over each era window in TWO variants:</t>
+          <t>PLUS the processor independently fits the Phillips form</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>- **constrained_b1**: `y = a + x^c` (Shaikh's published form, implicit b=1)</t>
+          <t>`y = a + b * x^c` over each era window in TWO variants:</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>- **unconstrained**: free three-parameter `y = a + b * x^c`</t>
+          <t>- **constrained_b1**: `y = a + x^c` (Shaikh's published form, implicit b=1)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1983-1993 transition omitted from both fits per Shaikh's convention</t>
+          <t>- **unconstrained**: free three-parameter `y = a + b * x^c`</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>(Phase 4 Q4 resolution). Sidecar JSON `S1405_phillips_fits.json` records</t>
+          <t>1983-1993 transition omitted from both fits per Shaikh's convention</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>both variants plus an additional pre-2008 era-2 fit (1994-2007) for Phase 6</t>
+          <t>(data-adequacy review). Sidecar JSON `S1405_phillips_fits.json` records</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>regime-stability assessment.</t>
+          <t>both variants plus an additional pre-2008 era-2 fit (1994-2007) for a later</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>enrichment pass's regime-stability assessment.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>## 5. Year coverage</t>
-        </is>
-      </c>
+      <c r="A39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>## 5. Year coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>1949-2011.</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr"/>
-    </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>## 6. Units</t>
-        </is>
-      </c>
+      <c r="A42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>## 6. Units</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>Decimal HP100 on both axes; Phillips parameters dimensionless.</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr"/>
-    </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>## 7. Caveats</t>
-        </is>
-      </c>
+      <c r="A45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1. **HP lambda=100** (Shaikh's annual default; Appendix 14.2 p. 893).</t>
+          <t>## 7. Caveats</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2. **Constrained vs unconstrained fits**: published reports a (C(1)) and c</t>
+          <t>1. **HP lambda=100** (Shaikh's annual default; Appendix 14.2 p. 893).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (C(3)) under implicit b=1. Phase 5 emits both for transparency.</t>
+          <t>2. **Constrained vs unconstrained fits**: published reports a (C(1)) and c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t xml:space="preserve">   (C(3)) under implicit b=1. This build emits both for transparency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>3. **1983-1993 transition**: omitted from primary fits.</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr"/>
-    </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>## 8. Cross-references</t>
-        </is>
-      </c>
+      <c r="A51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CD `S072`. Book p. 666-668. Published era-1: a=-1.026431, c=-0.010677,</t>
+          <t>## 8. Cross-references</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>Predecessor build: `S072`. Book p. 666-668. Published era-1: a=-1.026431, c=-0.010677,</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>R²=0.931; era-2: a=-1.010996, c=-0.003709, R²=0.965.</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr"/>
-    </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>## 9. Validation expectation</t>
-        </is>
-      </c>
+      <c r="A55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>±1.0% pass-through on the time series; ±0.05 absolute on fitted (a, c)</t>
+          <t>## 9. Validation expectation</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>±1.0% pass-through on the time series; ±0.05 absolute on fitted (a, c)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>parameters vs published.</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="4">
+    <row r="61">
+      <c r="A61" s="4">
         <f>== EPR: S1405_EPR.md ===</f>
         <v/>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t># S1405 — Extension Provenance Record</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr"/>
-    </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>**Ch 14 · Authored 2026-05-18**</t>
-        </is>
-      </c>
+      <c r="A63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr"/>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>**Chapter 14 · Authored 2026-05-18**</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>## Classification</t>
-        </is>
-      </c>
+      <c r="A65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>`content_type: time_series` · `construction: direct` (HP-filtered observed</t>
+          <t>## Classification</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>inputs + fitted curves). Extension via S1401/S1402 components, re-filtered</t>
+          <t>`content_type: time_series` · `construction: direct` (Hodrick-Prescott (HP)-filtered observed</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>inputs + fitted curves). Extension via S1401/S1402 components, re-filtered</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
           <t>over the full sample.</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr"/>
-    </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>## Method</t>
-        </is>
-      </c>
+      <c r="A70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Phase 5: replicate the published constrained b=1 fits. Phase 6: re-fit on</t>
+          <t>## Method</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1949-1982 and (extended) 1994-2024, plus a separate 1994-2007 era-2 fit for</t>
+          <t>This build replicates the published constrained b=1 fits; a later enrichment pass</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>regime-stability assessment per Q4 resolution.</t>
+          <t>could re-fit on 1949-1982 and (extended) 1994-2024, plus a separate 1994-2007 era-2 fit for</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr"/>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>regime-stability assessment per the data-adequacy review.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>## Dual Phillips fit</t>
-        </is>
-      </c>
+      <c r="A75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BOTH variants are emitted to `Technical/data/processed/S1405_phillips_fits.json`:</t>
+          <t>## Dual Phillips fit</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>- `constrained_b1`: replicates Shaikh's published form `y = a + x^c`</t>
+          <t>BOTH variants are emitted to `Technical/data/processed/S1405_phillips_fits.json`:</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>- `unconstrained`: free three-parameter `y = a + b * x^c`</t>
+          <t>- `constrained_b1`: replicates Shaikh's published form `y = a + x^c`</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>- `unconstrained`: free three-parameter `y = a + b * x^c`</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
           <t>Comparison documented in the validator report.</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr"/>
-    </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>## No-Proxy / No-Synthetic disclosures</t>
-        </is>
-      </c>
+      <c r="A81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>## No-Proxy / No-Synthetic disclosures</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
           <t>Inherits from S1401 and S1402.</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="inlineStr"/>
-    </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>## Failure-mode table</t>
-        </is>
-      </c>
+      <c r="A84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>| Mode | Trigger | Behaviour |</t>
+          <t>## Failure-mode table</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>|---|---|---|</t>
+          <t>| Mode | Trigger | Behaviour |</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>| curve_fit non-convergence | numerical | Returns `converged: false` with NaN params; doesn't fail pipeline |</t>
+          <t>|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>| curve_fit non-convergence | numerical | Returns `converged: false` with NaN params; doesn't fail pipeline |</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
           <t>| era window has &lt; 4 obs | very short window | Returns `converged: false` |</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="inlineStr"/>
-    </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>## CD2 divergence pre-disclosure</t>
-        </is>
-      </c>
+      <c r="A90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Minor; CD2 only emitted scatter, not fits.</t>
+          <t>## Divergence from the predecessor build</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Minor; the predecessor build only emitted scatter, not fits.</t>
         </is>
       </c>
     </row>
@@ -8547,7 +8550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -8712,7 +8715,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-05-18T23:19:03.878242+00:00</t>
+          <t>2026-07-02T06:19:06.560041+00:00</t>
         </is>
       </c>
     </row>
@@ -8725,6 +8728,18 @@
       <c r="B17" t="inlineStr">
         <is>
           <t>{"era1": {"fitted": {"a": -1.0264314084942405, "c": -0.010676501931369086, "r2": 0.9308709119788912, "n": 34, "converged": true}, "published": {"a": -1.026431, "c": -0.010677, "r2": 0.931}, "a_abs_diff": 4.0849424043365445e-07, "c_abs_diff": 4.980686309150051e-07, "r2_abs_diff": 0.00012908802110889184, "param_tol_abs": 0.05, "matches_published": true, "unconstrained": {"a": -0.00412605830878613, "b": 6.246071511159723e-05, "c": -1.705913249493028, "r2": 0.987531392983579, "n": 34, "converged": true}}, "era2": {"fitted": {"a": -1.0109957889204761, "c": -0.003708829519245551, "r2": 0.9649650111322942, "n": 18, "converged": true}, "published": {"a": -1.010996, "c": -0.003709, "r2": 0.965}, "a_abs_diff": 2.1107952385968076e-07, "c_abs_diff": 1.704807544491288e-07, "r2_abs_diff": 3.498886770580967e-05, "param_tol_abs": 0.05, "matches_published": true, "unconstrained": {"a": -5.218114246257406, "b": 5.207096707313747, "c": -0.0007166129112659367, "r2": 0.964983136239133, "n": 18, "converged": true}}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>independent_anchor_checks</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>{"status": "PASS", "red_checks": [], "anchors": {"status": "GREEN", "sid": "S1405", "n_anchors": 3, "n_red": 0, "n_green": 3, "n_na": 0, "anchors": [{"anchor_id": "S1405_phillips_a", "anchor_type": "derived_statistic", "subseries_id": "S1405-A", "source_description": "Book Phillips-curve regression (Fig 14.14, era 1 1949-1982): intercept a of Shaikh's constrained form y = a + x^c (implicit b=1, EViews NLLS). y=GWSHHP100 wage-share growth (S1405-A), x=ULINTENSITYHP100 unemployment intensity (S1405-B). Printed a=-1.026431.", "status": "GREEN", "expected": -1.026431, "actual": -1.02643141, "abs_pct_diff": 4e-05, "tolerance_pct": 1.0, "detail": "power_b1(NLLS) n=34 a=-1.026431 c=-0.010677 r2=0.930871"}, {"anchor_id": "S1405_phillips_c", "anchor_type": "derived_statistic", "subseries_id": "S1405-A", "source_description": "Book Phillips-curve regression (Fig 14.14, era 1): power-law exponent c of y = a + x^c. Printed c=-0.010677.", "status": "GREEN", "expected": -0.010677, "actual": -0.0106765, "abs_pct_diff": 0.004665, "tolerance_pct": 1.0, "detail": "power_b1(NLLS) n=34 a=-1.026431 c=-0.010677 r2=0.930871"}, {"anchor_id": "S1405_phillips_r2", "anchor_type": "derived_statistic", "subseries_id": "S1405-A", "source_description": "Book Phillips-curve regression (Fig 14.14, era 1): R^2 of the constrained fit y = a + x^c. Printed R^2=0.931.", "status": "GREEN", "expected": 0.931, "actual": 0.93087091, "abs_pct_diff": 0.013866, "tolerance_pct": 1.0, "detail": "power_b1(NLLS) n=34 a=-1.026431 c=-0.010677 r2=0.930871"}]}, "splice": {"status": "NA", "sid": "S1405", "splice_year": 2012, "detail": "no subseries spans 2011-&gt;2012"}, "plausibility": {"status": "NA", "sid": "S1405", "n_rules": 0, "rules": [], "detail": "no plausibility_rules registered"}}</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S1405_extenbook.xlsx
+++ b/extenbooks/S1405_extenbook.xlsx
@@ -8715,7 +8715,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-02T06:19:06.560041+00:00</t>
+          <t>2026-07-11T03:44:23.098151+00:00</t>
         </is>
       </c>
     </row>
@@ -8739,7 +8739,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{"status": "PASS", "red_checks": [], "anchors": {"status": "GREEN", "sid": "S1405", "n_anchors": 3, "n_red": 0, "n_green": 3, "n_na": 0, "anchors": [{"anchor_id": "S1405_phillips_a", "anchor_type": "derived_statistic", "subseries_id": "S1405-A", "source_description": "Book Phillips-curve regression (Fig 14.14, era 1 1949-1982): intercept a of Shaikh's constrained form y = a + x^c (implicit b=1, EViews NLLS). y=GWSHHP100 wage-share growth (S1405-A), x=ULINTENSITYHP100 unemployment intensity (S1405-B). Printed a=-1.026431.", "status": "GREEN", "expected": -1.026431, "actual": -1.02643141, "abs_pct_diff": 4e-05, "tolerance_pct": 1.0, "detail": "power_b1(NLLS) n=34 a=-1.026431 c=-0.010677 r2=0.930871"}, {"anchor_id": "S1405_phillips_c", "anchor_type": "derived_statistic", "subseries_id": "S1405-A", "source_description": "Book Phillips-curve regression (Fig 14.14, era 1): power-law exponent c of y = a + x^c. Printed c=-0.010677.", "status": "GREEN", "expected": -0.010677, "actual": -0.0106765, "abs_pct_diff": 0.004665, "tolerance_pct": 1.0, "detail": "power_b1(NLLS) n=34 a=-1.026431 c=-0.010677 r2=0.930871"}, {"anchor_id": "S1405_phillips_r2", "anchor_type": "derived_statistic", "subseries_id": "S1405-A", "source_description": "Book Phillips-curve regression (Fig 14.14, era 1): R^2 of the constrained fit y = a + x^c. Printed R^2=0.931.", "status": "GREEN", "expected": 0.931, "actual": 0.93087091, "abs_pct_diff": 0.013866, "tolerance_pct": 1.0, "detail": "power_b1(NLLS) n=34 a=-1.026431 c=-0.010677 r2=0.930871"}]}, "splice": {"status": "NA", "sid": "S1405", "splice_year": 2012, "detail": "no subseries spans 2011-&gt;2012"}, "plausibility": {"status": "NA", "sid": "S1405", "n_rules": 0, "rules": [], "detail": "no plausibility_rules registered"}}</t>
+          <t>{"status": "PASS", "red_checks": [], "anchors": {"status": "GREEN", "sid": "S1405", "n_anchors": 3, "n_red": 0, "n_green": 3, "n_na": 0, "anchors": [{"anchor_id": "S1405_phillips_a", "anchor_type": "derived_statistic", "subseries_id": "S1405-A", "source_description": "Book Phillips-curve regression (Fig 14.14, era 1 1949-1982): intercept a of Shaikh's constrained form y = a + x^c (implicit b=1, EViews NLLS). y=GWSHHP100 wage-share growth (S1405-A), x=ULINTENSITYHP100 unemployment intensity (S1405-B). Printed a=-1.026431.", "status": "GREEN", "expected": -1.026431, "actual": -1.02643141, "abs_pct_diff": 4e-05, "tolerance_pct": 1.0, "detail": "power_b1(NLLS) n=34 a=-1.026431 c=-0.010677 r2=0.930871"}, {"anchor_id": "S1405_phillips_c", "anchor_type": "derived_statistic", "subseries_id": "S1405-A", "source_description": "Book Phillips-curve regression (Fig 14.14, era 1): power-law exponent c of y = a + x^c. Printed c=-0.010677.", "status": "GREEN", "expected": -0.010677, "actual": -0.0106765, "abs_pct_diff": 0.004665, "tolerance_pct": 1.0, "detail": "power_b1(NLLS) n=34 a=-1.026431 c=-0.010677 r2=0.930871"}, {"anchor_id": "S1405_phillips_r2", "anchor_type": "derived_statistic", "subseries_id": "S1405-A", "source_description": "Book Phillips-curve regression (Fig 14.14, era 1): R^2 of the constrained fit y = a + x^c. Printed R^2=0.931.", "status": "GREEN", "expected": 0.931, "actual": 0.93087091, "abs_pct_diff": 0.013866, "tolerance_pct": 1.0, "detail": "power_b1(NLLS) n=34 a=-1.026431 c=-0.010677 r2=0.930871"}]}, "splice": {"status": "NA", "sid": "S1405", "detail": "no extension / no book+extension ranges"}, "plausibility": {"status": "NA", "sid": "S1405", "n_rules": 0, "rules": [], "detail": "no plausibility_rules registered"}}</t>
         </is>
       </c>
     </row>
@@ -8754,11 +8754,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8781,6 +8781,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_APPENDIX_14_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>book_verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Reconstructs Shaikh (2016) Ch.14 Figure 14.14 (HP(100)-Filtered Values, Rate of Change of the Wage Share versus Unemployment Intensity, United States, 1949-2011) -- the central empirical result of Ch.14: a stable two-era wage-share Phillips curve with the post-1983 segment shifted down. Real data present in chopped CSV (255 points, 4 subseries incl. 2 fitted curves); book_period_validated; figure number and quotes KB-verified (Fig 14.14 quote verbatim at ch14 KB line 1537/1502). The two published constrained-b=1 fits were cross-checked against the Appendix 14.2 EViews output in ch18 KB: era-1 (1949-1982) C(1)=-1.026431, C(3)=-0.010677, R2=0.930871; era-2 (1994-2011) C(1)=-1.010996, C(3)=-0.003709, R2=0.964965 -- all match the research JSON exactly. FAITHFUL-TRANSCRIPTION NOTE (not an error): the method quote in S1405_research.json reads 'figure 14.4 of chapter 14' -- this is Shaikh's OWN typo in Appendix 14.2 (verified verbatim at ch18 KB line 8624); he means Figure 14.14. The transcription is faithful; the explainer uses the clean ch14 Fig 14.14 quote instead to avoid propagating the appendix typo.", "date": "2026-06-11"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1405_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1405_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Central empirical Phillips curve result of Ch14. Phase 5 emits both constrained b=1 and unconstrained fits per Q3 resolution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>time_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>decimal_hp100</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
